--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="841">
   <si>
     <t>Property</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240329120000</t>
+    <t>20241120120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2024-11-20T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2305,10 +2305,16 @@
     <t>329</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>Coordonnateur de parcours</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Secrétaire médicale</t>
+    <t>Secrétaire assistante médico-administrative</t>
   </si>
   <si>
     <t>333</t>
@@ -2335,6 +2341,90 @@
     <t>Gestionnaire alertes et urgences sanitaires</t>
   </si>
   <si>
+    <t>336</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans l'accueil et l'orientation des personnes</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la logistique</t>
+  </si>
+  <si>
+    <t>338</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans l'hôtellerie et la restauration</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction de la qualité, hygiène, sécurité et environnement</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des systèmes d'information</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des finances et comptabilité</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction de la communication</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des ressources humaines</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des affaires médicales</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans le social, éducatif, psychologie et culturel</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>Etudiant - infirmier</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>Etudiant - aide-soignant</t>
+  </si>
+  <si>
+    <t>348</t>
+  </si>
+  <si>
+    <t>Etudiant - auxiliaire de puériculture</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>Etudiant - masseur-kinésithérapeute</t>
+  </si>
+  <si>
     <t>350</t>
   </si>
   <si>
@@ -2345,6 +2435,108 @@
   </si>
   <si>
     <t>Assistant(e) maternel(le)</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>Externe en médecine</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>Externe en odontologie</t>
+  </si>
+  <si>
+    <t>356</t>
+  </si>
+  <si>
+    <t>Externe en maïeutique</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>Externe en pharmacie</t>
+  </si>
+  <si>
+    <t>358</t>
+  </si>
+  <si>
+    <t>Autre étudiant</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>Directeur d'établissement</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>Brancardier</t>
+  </si>
+  <si>
+    <t>361</t>
+  </si>
+  <si>
+    <t>Educateur en activité physique adaptée</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>Technicien d'informations médicales</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>Attaché de recherche clinique</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>Praticien A Diplôme Hors Union Européenne (PADHUE)</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>Gestionnaire admissions / frais de séjour / traitement externe</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>Archiviste</t>
+  </si>
+  <si>
+    <t>367</t>
+  </si>
+  <si>
+    <t>Surveillant de nuit</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>Animateur</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>Biologiste médical non-médecin</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Opérateur de Soins Non Programmés</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge</t>
@@ -5497,7 +5689,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -5810,18 +6002,274 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>44</v>
+        <v>776</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>44</v>
+        <v>777</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="B40" t="s" s="2">
-        <v>776</v>
+      <c r="B72" t="s" s="2">
+        <v>840</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="829">
   <si>
     <t>Property</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241120120000</t>
+    <t>20241210120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T12:00:00+01:00</t>
+    <t>2024-12-10T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2089,220 +2089,184 @@
     <t>Psychologue</t>
   </si>
   <si>
-    <t>97</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R95-UsagerTitre/FHIR/TRE-R95-UsagerTitre</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Assistant de service social</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R94-ProfessionSocial/FHIR/TRE-R94-ProfessionSocial</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Assistant de service social (PAERPA)</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>Coordination territoriale d'appui (PAERPA)</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>Aide et accompagnement à domicile (PAERPA)</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Avocat participant aux processus de soins sans consentement (eSSS)</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Assistant de service social (Expérimentation MAIA)</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>Psychologue (Expérimentation MAIA)</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Psychothérapeute (Expérimentation MAIA)</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Mandataire judiciaire à la protection des majeurs (MJPM)</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Pilote MAIA</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Gestionnaire de cas MAIA</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Equipe médico-sociale APA</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Autre acteur mettant en oeuvre la méthode MAIA</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Autre professionnel</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>Préparateur en pharmacie (officine)</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>Auxiliaire de vie sociale</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>Technicien de l'intervention sociale et familiale</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Conseiller en économie sociale et familiale</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Médiateur familial</t>
+  </si>
+  <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>Assistant familial</t>
+  </si>
+  <si>
+    <t>323</t>
+  </si>
+  <si>
+    <t>Aide médico-psychologique (AMP)</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
+    <t>Moniteur éducateur</t>
+  </si>
+  <si>
+    <t>325</t>
+  </si>
+  <si>
+    <t>Educateur de jeunes enfants</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>Educateur spécialisé</t>
+  </si>
+  <si>
+    <t>327</t>
+  </si>
+  <si>
+    <t>Educateur technique spécialisé</t>
+  </si>
+  <si>
+    <t>328</t>
+  </si>
+  <si>
+    <t>Accompagnant éducatif et social</t>
+  </si>
+  <si>
+    <t>329</t>
   </si>
   <si>
     <t>Conseiller en génétique</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R95-UsagerTitre/FHIR/TRE-R95-UsagerTitre</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Assistant de service social</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>Auxiliaire de vie sociale</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>Technicien de l'intervention sociale et familiale</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>Conseiller en économie sociale et familiale</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>Médiateur familial</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>Assistant familial</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>Aide médico-psychologique (AMP)</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>Moniteur éducateur</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>Educateur de jeunes enfants</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>Educateur spécialisé</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>Educateur technique spécialisé</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>Accompagnant éducatif et social</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R94-ProfessionSocial/FHIR/TRE-R94-ProfessionSocial</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>Assistant de service social (PAERPA)</t>
-  </si>
-  <si>
-    <t>301</t>
-  </si>
-  <si>
-    <t>Coordination territoriale d'appui (PAERPA)</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>Aide et accompagnement à domicile (PAERPA)</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>Avocat participant aux processus de soins sans consentement (eSSS)</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>Assistant de service social (Expérimentation MAIA)</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>Psychologue (Expérimentation MAIA)</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>Psychothérapeute (Expérimentation MAIA)</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Mandataire judiciaire à la protection des majeurs (MJPM)</t>
-  </si>
-  <si>
-    <t>308</t>
-  </si>
-  <si>
-    <t>Pilote MAIA</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>Gestionnaire de cas MAIA</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Equipe médico-sociale APA</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Autre acteur mettant en oeuvre la méthode MAIA</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>Autre professionnel</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>314</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>316</t>
-  </si>
-  <si>
-    <t>317</t>
-  </si>
-  <si>
-    <t>Préparateur en pharmacie (officine)</t>
-  </si>
-  <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>322</t>
-  </si>
-  <si>
-    <t>323</t>
-  </si>
-  <si>
-    <t>324</t>
-  </si>
-  <si>
-    <t>325</t>
-  </si>
-  <si>
-    <t>326</t>
-  </si>
-  <si>
-    <t>327</t>
-  </si>
-  <si>
-    <t>328</t>
-  </si>
-  <si>
-    <t>329</t>
   </si>
   <si>
     <t>330</t>
@@ -5477,7 +5441,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -5526,26 +5490,18 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>690</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>691</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -5555,7 +5511,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -5572,114 +5528,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>695</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>696</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>697</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>717</v>
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -5706,111 +5574,111 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>718</v>
+        <v>694</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>719</v>
+        <v>695</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>720</v>
+        <v>696</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>721</v>
+        <v>697</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>722</v>
+        <v>698</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>723</v>
+        <v>699</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>724</v>
+        <v>700</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>725</v>
+        <v>701</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>726</v>
+        <v>702</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>727</v>
+        <v>703</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>728</v>
+        <v>704</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>729</v>
+        <v>705</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>730</v>
+        <v>706</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>731</v>
+        <v>707</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>732</v>
+        <v>708</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>733</v>
+        <v>709</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>734</v>
+        <v>710</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>735</v>
+        <v>711</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>736</v>
+        <v>712</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>737</v>
+        <v>713</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>738</v>
+        <v>714</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>739</v>
+        <v>715</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>741</v>
+        <v>717</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>742</v>
+        <v>718</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>743</v>
+        <v>719</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>744</v>
+        <v>720</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>612</v>
@@ -5818,7 +5686,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>745</v>
+        <v>721</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>614</v>
@@ -5826,7 +5694,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>746</v>
+        <v>722</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>616</v>
@@ -5834,7 +5702,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>747</v>
+        <v>723</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>618</v>
@@ -5842,418 +5710,418 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>748</v>
+        <v>724</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>749</v>
+        <v>725</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>750</v>
+        <v>726</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>696</v>
+        <v>727</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>751</v>
+        <v>728</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>698</v>
+        <v>729</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>752</v>
+        <v>730</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>700</v>
+        <v>731</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>702</v>
+        <v>733</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>754</v>
+        <v>734</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>704</v>
+        <v>735</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>755</v>
+        <v>736</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>706</v>
+        <v>737</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>708</v>
+        <v>739</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>757</v>
+        <v>740</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>710</v>
+        <v>741</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>758</v>
+        <v>742</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>712</v>
+        <v>743</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>759</v>
+        <v>744</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>714</v>
+        <v>745</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>716</v>
+        <v>747</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>691</v>
+        <v>749</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>763</v>
+        <v>751</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>765</v>
+        <v>753</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>767</v>
+        <v>755</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>769</v>
+        <v>757</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>771</v>
+        <v>759</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>773</v>
+        <v>761</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>775</v>
+        <v>763</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>777</v>
+        <v>765</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>779</v>
+        <v>767</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>781</v>
+        <v>769</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>783</v>
+        <v>771</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>785</v>
+        <v>773</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>786</v>
+        <v>774</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>787</v>
+        <v>775</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>789</v>
+        <v>777</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>791</v>
+        <v>779</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>793</v>
+        <v>781</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>794</v>
+        <v>782</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>795</v>
+        <v>783</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>797</v>
+        <v>785</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>799</v>
+        <v>787</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>801</v>
+        <v>789</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>803</v>
+        <v>791</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>805</v>
+        <v>793</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>807</v>
+        <v>795</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>809</v>
+        <v>797</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>811</v>
+        <v>799</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>813</v>
+        <v>801</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>815</v>
+        <v>803</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>816</v>
+        <v>804</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>817</v>
+        <v>805</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>818</v>
+        <v>806</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>819</v>
+        <v>807</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>821</v>
+        <v>809</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>823</v>
+        <v>811</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>825</v>
+        <v>813</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>827</v>
+        <v>815</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>831</v>
+        <v>819</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>833</v>
+        <v>821</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>835</v>
+        <v>823</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>839</v>
+        <v>827</v>
       </c>
     </row>
     <row r="71">
@@ -6269,7 +6137,7 @@
         <v>45</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>840</v>
+        <v>828</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="819">
   <si>
     <t>Property</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241210120000</t>
+    <t>20241211120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T12:00:00+01:00</t>
+    <t>2024-12-11T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -766,366 +766,6 @@
     <t>Médecin - Urologie (CEX)</t>
   </si>
   <si>
-    <t>G15_10/SCH01</t>
-  </si>
-  <si>
-    <t>Médecin - Anatomie et cytologie pathologiques (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH02</t>
-  </si>
-  <si>
-    <t>Médecin - Anesthésie-réanimation (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH03</t>
-  </si>
-  <si>
-    <t>Médecin - Bactériologie-virologie, hygiène hosp (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH04</t>
-  </si>
-  <si>
-    <t>Médecin - Biochimie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH05</t>
-  </si>
-  <si>
-    <t>Médecin - Biologie cellulaire, histologie, bio du dév (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH06</t>
-  </si>
-  <si>
-    <t>Médecin - Biologie médicale (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH07</t>
-  </si>
-  <si>
-    <t>Médecin - Biophysique (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH08</t>
-  </si>
-  <si>
-    <t>Médecin - Oncologie médicale (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH09</t>
-  </si>
-  <si>
-    <t>Médecin - Cardiologie et maladies vasculaires (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH10</t>
-  </si>
-  <si>
-    <t>Médecin - Chirurgie générale (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH11</t>
-  </si>
-  <si>
-    <t>Médecin - Chirurgie viscérale et digestive (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH12</t>
-  </si>
-  <si>
-    <t>Médecin - Chirurgie infantile (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH13</t>
-  </si>
-  <si>
-    <t>Médecin - Chirurgie maxillo-faciale (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH14</t>
-  </si>
-  <si>
-    <t>Médecin - Chirurgie orthopédique et Traumatologique (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH15</t>
-  </si>
-  <si>
-    <t>Médecin - Chirurgie plast reconstruct, esthétique (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH16</t>
-  </si>
-  <si>
-    <t>Médecin - Chirurgie thoracique et cardio-vasculaire (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH17</t>
-  </si>
-  <si>
-    <t>Médecin - Chirurgie urologique (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH18</t>
-  </si>
-  <si>
-    <t>Médecin - Chirurgie vasculaire (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH19</t>
-  </si>
-  <si>
-    <t>Médecin - Dermatologie et Vénéréologie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH20</t>
-  </si>
-  <si>
-    <t>Médecin - Endocrinologie et Métabolisme (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH21</t>
-  </si>
-  <si>
-    <t>Médecin - Santé publique (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH22</t>
-  </si>
-  <si>
-    <t>Médecin - Explorations fonctionnelles (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH23</t>
-  </si>
-  <si>
-    <t>Médecin - Gastro-entérologie et Hépatologie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH24</t>
-  </si>
-  <si>
-    <t>Médecin - Génétique (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH25</t>
-  </si>
-  <si>
-    <t>Médecin - Génétique médicale (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH26</t>
-  </si>
-  <si>
-    <t>Médecin - Gynécologie et Obstétrique (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH27</t>
-  </si>
-  <si>
-    <t>Médecin - Hématologie biologique (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH28</t>
-  </si>
-  <si>
-    <t>Médecin - Hématologie clinique (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH29</t>
-  </si>
-  <si>
-    <t>Médecin - Hémobiologie-transfusion (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH30</t>
-  </si>
-  <si>
-    <t>Médecin - Hygiène hospitalière (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH31</t>
-  </si>
-  <si>
-    <t>Médecin - Immunologie biologique (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH32</t>
-  </si>
-  <si>
-    <t>Médecin - Immunologie clinique (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH33</t>
-  </si>
-  <si>
-    <t>Médecin - Maladies infectieuses, maladies tropicales (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH34</t>
-  </si>
-  <si>
-    <t>Médecin - Médecine de la repro et Gynécologie médicale (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH35</t>
-  </si>
-  <si>
-    <t>Médecin - Médecine du travail (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH36</t>
-  </si>
-  <si>
-    <t>Médecin - Médecine d'urgence (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH37</t>
-  </si>
-  <si>
-    <t>Médecin - Médecine générale (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH38</t>
-  </si>
-  <si>
-    <t>Médecin - Gériatrie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH39</t>
-  </si>
-  <si>
-    <t>Médecin - Médecine interne (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH40</t>
-  </si>
-  <si>
-    <t>Médecin - Médecine légale (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH41</t>
-  </si>
-  <si>
-    <t>Médecin - Médecine nucléaire (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH42</t>
-  </si>
-  <si>
-    <t>Médecin - Médecine physique et de réadaptation (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH43</t>
-  </si>
-  <si>
-    <t>Médecin - Néphrologie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH44</t>
-  </si>
-  <si>
-    <t>Médecin - neuro-chirurgie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH45</t>
-  </si>
-  <si>
-    <t>Médecin - Neurologie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH46</t>
-  </si>
-  <si>
-    <t>Médecin - Odontologie polyvalente (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH47</t>
-  </si>
-  <si>
-    <t>Médecin - Ophtalmologie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH48</t>
-  </si>
-  <si>
-    <t>Médecin - Oto-rhino-laryngologie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH49</t>
-  </si>
-  <si>
-    <t>Médecin - Parasitologie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH50</t>
-  </si>
-  <si>
-    <t>Médecin - Pédiatrie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH51</t>
-  </si>
-  <si>
-    <t>Médecin - Pharmacie polyvalente et Pharmacie hosp (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH52</t>
-  </si>
-  <si>
-    <t>Médecin - Pharmacologie clinique et Toxicologie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH53</t>
-  </si>
-  <si>
-    <t>Médecin - Pneumologie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH54</t>
-  </si>
-  <si>
-    <t>Médecin - Psychiatrie polyvalente (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH55</t>
-  </si>
-  <si>
-    <t>Médecin - Radiologie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH56</t>
-  </si>
-  <si>
-    <t>Médecin - Oncologie radiothérapique (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH57</t>
-  </si>
-  <si>
-    <t>Médecin - Réanimation médicale (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH58</t>
-  </si>
-  <si>
-    <t>Médecin - Rhumatologie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH59</t>
-  </si>
-  <si>
-    <t>Médecin - Stomatologie (SCH)</t>
-  </si>
-  <si>
-    <t>G15_10/SCH60</t>
-  </si>
-  <si>
-    <t>Médecin - Toxicologie et Pharmacologie (SCH)</t>
-  </si>
-  <si>
     <t>G15_10/C01</t>
   </si>
   <si>
@@ -1726,6 +1366,348 @@
     <t>Médecin - Cancérologie, opt Imagerie cancérologie (DNQ)</t>
   </si>
   <si>
+    <t>G15_10/80</t>
+  </si>
+  <si>
+    <t>Médecin - Homéopathie (OP)</t>
+  </si>
+  <si>
+    <t>G15_10/81</t>
+  </si>
+  <si>
+    <t>Médecin - Acupuncture (OP)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC01</t>
+  </si>
+  <si>
+    <t>Médecin - Addictologie (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC02</t>
+  </si>
+  <si>
+    <t>Médecin - Allergologie et immunologie clinique (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC03</t>
+  </si>
+  <si>
+    <t>Médecin - Andrologie (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC04</t>
+  </si>
+  <si>
+    <t>Médecin - Cancérologie option traitements médicaux des cancers (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC05</t>
+  </si>
+  <si>
+    <t>Médecin - Cancérologie option chiruggie cancérologique (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC06</t>
+  </si>
+  <si>
+    <t>Médecin - Cancérologie option réseaux de cancérologie (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC07</t>
+  </si>
+  <si>
+    <t>Médecin - Cancérologie option biologie en cancérologie (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC08</t>
+  </si>
+  <si>
+    <t>Médecin - Cancérologie option imagerie en cancérologie (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC09</t>
+  </si>
+  <si>
+    <t>Médecin - Dermatopathologie (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC10</t>
+  </si>
+  <si>
+    <t>Médecin - Foetopathologie (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC11</t>
+  </si>
+  <si>
+    <t>Médecin - Hémobiologie - tranfusion (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC12</t>
+  </si>
+  <si>
+    <t>Médecin - Médecine de la douleur et médecine palliative (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC13</t>
+  </si>
+  <si>
+    <t>Médecin - Médecine de la reproduction (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC14</t>
+  </si>
+  <si>
+    <t>Médecin - Médecine d'urgence (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC15</t>
+  </si>
+  <si>
+    <t>Médecin - Médecine du sport (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC16</t>
+  </si>
+  <si>
+    <t>Médecin - Médecine légale et expertises médicales (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC17</t>
+  </si>
+  <si>
+    <t>Médecin - Médecine vasculaire (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC18</t>
+  </si>
+  <si>
+    <t>Médecin - Néonatologie (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC19</t>
+  </si>
+  <si>
+    <t>Médecin - Neuropathologie (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC20</t>
+  </si>
+  <si>
+    <t>Médecin - Nutrition (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC21</t>
+  </si>
+  <si>
+    <t>Médecin - Orthopédie dento-maxillo-faciale (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC22</t>
+  </si>
+  <si>
+    <t>Médecin - Pathologie infectieuse et tropicale, clinique et biologique (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC23</t>
+  </si>
+  <si>
+    <t>Médecin - Pharmacologie clinique et évaluation des thérapeutiques (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/DEC24</t>
+  </si>
+  <si>
+    <t>Médecin - Psychiatrie de l'enfant et de l'adolescent (DEC)</t>
+  </si>
+  <si>
+    <t>G15_10/SST01</t>
+  </si>
+  <si>
+    <t>Médecin - Addictologie (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST02</t>
+  </si>
+  <si>
+    <t>Médecin - Bio-informatique médicale (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST03</t>
+  </si>
+  <si>
+    <t>Médecin - Cancérologie déc. hémato-cancérologie pédiatrique (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST04</t>
+  </si>
+  <si>
+    <t>Médecin - Cancérologie traitements médicaux des cancers (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST05</t>
+  </si>
+  <si>
+    <t>Médecin - Cardiologie pédiatrique et congénitale (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST06</t>
+  </si>
+  <si>
+    <t>Médecin - Chirurgie de la main (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST07</t>
+  </si>
+  <si>
+    <t>Médecin - Chirurgie en situation de guerre ou de catastrophe (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST08</t>
+  </si>
+  <si>
+    <t>Médecin - Chirurgie orbito-palpébro-lacrymale (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST09</t>
+  </si>
+  <si>
+    <t>Médecin - Douleur (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST10</t>
+  </si>
+  <si>
+    <t>Médecin - Expertise médicale-préjudice corporel (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST11</t>
+  </si>
+  <si>
+    <t>Médecin - Foetopathologie (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST12</t>
+  </si>
+  <si>
+    <t>Médecin - Génétique et médecine moléculaire bioclinique (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST13</t>
+  </si>
+  <si>
+    <t>Médecin - Hématologie bioclinique (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST14</t>
+  </si>
+  <si>
+    <t>Médecin - Hygiène-prévention de l'infection, résistances (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST15</t>
+  </si>
+  <si>
+    <t>Médecin - Maladies allergiques (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST16</t>
+  </si>
+  <si>
+    <t>Médecin - Médecine hospitalière polyvalente (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST17</t>
+  </si>
+  <si>
+    <t>Médecin - Médecine palliative (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST18</t>
+  </si>
+  <si>
+    <t>Médecin - Médecine scolaire (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST19</t>
+  </si>
+  <si>
+    <t>Médecin - Médecine en situation de guerre ou en SSE (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST20</t>
+  </si>
+  <si>
+    <t>Médecin - Médecine et biologie de la reproduction-andrologie (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST21</t>
+  </si>
+  <si>
+    <t>Médecin - Médecine du sport (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST22</t>
+  </si>
+  <si>
+    <t>Médecin - Nutrition appliquée (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST23</t>
+  </si>
+  <si>
+    <t>Médecin - Pharmacologie médicale/thérapeutique (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST24</t>
+  </si>
+  <si>
+    <t>Médecin - Sommeil (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST25</t>
+  </si>
+  <si>
+    <t>Médecin - Thérapie cellulaire/transfusion (SST)</t>
+  </si>
+  <si>
+    <t>G15_10/SST26</t>
+  </si>
+  <si>
+    <t>Médecin - Urgences pédiatriques (SST)</t>
+  </si>
+  <si>
+    <t>G15_21/FQ01</t>
+  </si>
+  <si>
+    <t>Pharmacien - Expérience prat. art. R.5124-16 du CSP Fabricant</t>
+  </si>
+  <si>
+    <t>G15_21/FQ02</t>
+  </si>
+  <si>
+    <t>Pharmacien - Expérience prat. art. R.5124-16 du CSP Exploitant</t>
+  </si>
+  <si>
+    <t>G15_21/FQ03</t>
+  </si>
+  <si>
+    <t>Pharmacien - Exp. prat. art. R.5124-16 du CSP Thérapie Cellulaire</t>
+  </si>
+  <si>
+    <t>G15_21/FQ04</t>
+  </si>
+  <si>
+    <t>Pharmacien - Expérience pratique article R.5124-18 du CSP</t>
+  </si>
+  <si>
+    <t>G15_21/FQ05</t>
+  </si>
+  <si>
+    <t>Pharmacien - Expérience pratique article R.5141-129 du CSP</t>
+  </si>
+  <si>
     <t>G15_21</t>
   </si>
   <si>
@@ -1852,345 +1834,327 @@
     <t>Physicien médical</t>
   </si>
   <si>
-    <t>G15_35</t>
+    <t>G15_40</t>
+  </si>
+  <si>
+    <t>Chirurgien-Dentiste</t>
+  </si>
+  <si>
+    <t>G15_40/SCD01</t>
+  </si>
+  <si>
+    <t>Chirurgien-Dentiste - Orthopédie dento-faciale (SCD)</t>
+  </si>
+  <si>
+    <t>G15_40/SCD02</t>
+  </si>
+  <si>
+    <t>Chirurgien-Dentiste - Chirurgie orale (SCD)</t>
+  </si>
+  <si>
+    <t>G15_40/SCD03</t>
+  </si>
+  <si>
+    <t>Chirurgien-Dentiste - Médecine bucco-dentaire (SCD)</t>
+  </si>
+  <si>
+    <t>G15_50</t>
+  </si>
+  <si>
+    <t>Sage-Femme</t>
+  </si>
+  <si>
+    <t>G15_60</t>
+  </si>
+  <si>
+    <t>Infirmier</t>
+  </si>
+  <si>
+    <t>G15_60/SI01</t>
+  </si>
+  <si>
+    <t>Infirmier - Exercice infirmier en pratique avancée pathologies chroniques stabilisées (SI)</t>
+  </si>
+  <si>
+    <t>G15_60/SI02</t>
+  </si>
+  <si>
+    <t>Infirmier - Exercice infirmier en pratique avancée oncologie et hémato-oncologie (SI)</t>
+  </si>
+  <si>
+    <t>G15_60/SI03</t>
+  </si>
+  <si>
+    <t>Infirmier - Exerc. infirmier pratique avancée maladie rénale chroniq.,dialyse,transp. rénale (SI)</t>
+  </si>
+  <si>
+    <t>G15_60/SI04</t>
+  </si>
+  <si>
+    <t>Infirmier - Exercice infirmier en pratique avancée santé mentale (SI)</t>
+  </si>
+  <si>
+    <t>G15_60/SI05</t>
+  </si>
+  <si>
+    <t>Infirmier - Exercice infirmier en pratique avancée urgences (SI)</t>
+  </si>
+  <si>
+    <t>G15_69</t>
+  </si>
+  <si>
+    <t>Infirmier psychiatrique</t>
+  </si>
+  <si>
+    <t>G15_70</t>
+  </si>
+  <si>
+    <t>Masseur-Kinésithérapeute</t>
+  </si>
+  <si>
+    <t>G15_80</t>
+  </si>
+  <si>
+    <t>Pédicure-Podologue</t>
+  </si>
+  <si>
+    <t>G15_81</t>
+  </si>
+  <si>
+    <t>Orthoprothésiste</t>
+  </si>
+  <si>
+    <t>G15_82</t>
+  </si>
+  <si>
+    <t>Podo-Orthésiste</t>
+  </si>
+  <si>
+    <t>G15_83</t>
+  </si>
+  <si>
+    <t>Orthopédiste-Orthésiste</t>
+  </si>
+  <si>
+    <t>G15_84</t>
+  </si>
+  <si>
+    <t>Oculariste</t>
+  </si>
+  <si>
+    <t>G15_85</t>
+  </si>
+  <si>
+    <t>Epithésiste</t>
+  </si>
+  <si>
+    <t>G15_86</t>
+  </si>
+  <si>
+    <t>Technicien de laboratoire médical</t>
+  </si>
+  <si>
+    <t>G15_91</t>
+  </si>
+  <si>
+    <t>Orthophoniste</t>
+  </si>
+  <si>
+    <t>G15_92</t>
+  </si>
+  <si>
+    <t>Orthoptiste</t>
+  </si>
+  <si>
+    <t>G15_94</t>
+  </si>
+  <si>
+    <t>Ergothérapeute</t>
+  </si>
+  <si>
+    <t>G15_95</t>
+  </si>
+  <si>
+    <t>Diététicien</t>
+  </si>
+  <si>
+    <t>G15_96</t>
+  </si>
+  <si>
+    <t>Psychomotricien</t>
+  </si>
+  <si>
+    <t>G15_98</t>
+  </si>
+  <si>
+    <t>Manipulateur ERM</t>
+  </si>
+  <si>
+    <t>G16_10</t>
+  </si>
+  <si>
+    <t>Médecin en formation</t>
+  </si>
+  <si>
+    <t>G16_21</t>
+  </si>
+  <si>
+    <t>Pharmacien en formation</t>
+  </si>
+  <si>
+    <t>G16_40</t>
+  </si>
+  <si>
+    <t>Chirurgien-Dentiste en formation</t>
+  </si>
+  <si>
+    <t>G16_50</t>
+  </si>
+  <si>
+    <t>Sage-Femme en formation</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A02-ProfessionSavFaire-CISIS/FHIR/TRE-A02-ProfessionSavFaire-CISIS</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>Ostéopathe</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>Psychothérapeute</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>Chiropracteur</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>Psychologue</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R95-UsagerTitre/FHIR/TRE-R95-UsagerTitre</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Assistant de service social</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R94-ProfessionSocial/FHIR/TRE-R94-ProfessionSocial</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Assistant de service social (PAERPA)</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>Coordination territoriale d'appui (PAERPA)</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>Aide et accompagnement à domicile (PAERPA)</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Avocat participant aux processus de soins sans consentement (eSSS)</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Assistant de service social (Expérimentation MAIA)</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>Psychologue (Expérimentation MAIA)</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Psychothérapeute (Expérimentation MAIA)</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Mandataire judiciaire à la protection des majeurs (MJPM)</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Pilote MAIA</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Gestionnaire de cas MAIA</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Equipe médico-sociale APA</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Autre acteur mettant en oeuvre la méthode MAIA</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Autre professionnel</t>
+  </si>
+  <si>
+    <t>313</t>
   </si>
   <si>
     <t>Aide-soignant</t>
   </si>
   <si>
-    <t>G15_36</t>
+    <t>314</t>
   </si>
   <si>
     <t>Ambulancier</t>
   </si>
   <si>
-    <t>G15_37</t>
+    <t>315</t>
   </si>
   <si>
     <t>Auxiliaire de puériculture</t>
   </si>
   <si>
-    <t>G15_38</t>
+    <t>316</t>
   </si>
   <si>
     <t>Préparateur en pharmacie hospitalière</t>
   </si>
   <si>
-    <t>G15_39</t>
-  </si>
-  <si>
-    <t>Préparateur en pharmacie</t>
-  </si>
-  <si>
-    <t>G15_40</t>
-  </si>
-  <si>
-    <t>Chirurgien-Dentiste</t>
-  </si>
-  <si>
-    <t>G15_40/SCD01</t>
-  </si>
-  <si>
-    <t>Chirurgien-Dentiste - Orthopédie dento-faciale (SCD)</t>
-  </si>
-  <si>
-    <t>G15_40/SCD02</t>
-  </si>
-  <si>
-    <t>Chirurgien-Dentiste - Chirurgie orale (SCD)</t>
-  </si>
-  <si>
-    <t>G15_40/SCD03</t>
-  </si>
-  <si>
-    <t>Chirurgien-Dentiste - Médecine bucco-dentaire (SCD)</t>
-  </si>
-  <si>
-    <t>G15_50</t>
-  </si>
-  <si>
-    <t>Sage-Femme</t>
-  </si>
-  <si>
-    <t>G15_60</t>
-  </si>
-  <si>
-    <t>Infirmier</t>
-  </si>
-  <si>
-    <t>G15_60/SI01</t>
-  </si>
-  <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée pathologies chroniques stabilisées (SI)</t>
-  </si>
-  <si>
-    <t>G15_60/SI02</t>
-  </si>
-  <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée oncologie et hémato-oncologie (SI)</t>
-  </si>
-  <si>
-    <t>G15_60/SI03</t>
-  </si>
-  <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée maladie rénale chronique, dialyse et transplantation rénale (SI)</t>
-  </si>
-  <si>
-    <t>G15_60/SI04</t>
-  </si>
-  <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée santé mentale (SI)</t>
-  </si>
-  <si>
-    <t>G15_60/SI05</t>
-  </si>
-  <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée urgences (SI)</t>
-  </si>
-  <si>
-    <t>G15_69</t>
-  </si>
-  <si>
-    <t>Infirmier psychiatrique</t>
-  </si>
-  <si>
-    <t>G15_70</t>
-  </si>
-  <si>
-    <t>Masseur-Kinésithérapeute</t>
-  </si>
-  <si>
-    <t>G15_80</t>
-  </si>
-  <si>
-    <t>Pédicure-Podologue</t>
-  </si>
-  <si>
-    <t>G15_81</t>
-  </si>
-  <si>
-    <t>Orthoprothésiste</t>
-  </si>
-  <si>
-    <t>G15_82</t>
-  </si>
-  <si>
-    <t>Podo-Orthésiste</t>
-  </si>
-  <si>
-    <t>G15_83</t>
-  </si>
-  <si>
-    <t>Orthopédiste-Orthésiste</t>
-  </si>
-  <si>
-    <t>G15_84</t>
-  </si>
-  <si>
-    <t>Oculariste</t>
-  </si>
-  <si>
-    <t>G15_85</t>
-  </si>
-  <si>
-    <t>Epithésiste</t>
-  </si>
-  <si>
-    <t>G15_86</t>
-  </si>
-  <si>
-    <t>Technicien de laboratoire médical</t>
-  </si>
-  <si>
-    <t>G15_91</t>
-  </si>
-  <si>
-    <t>Orthophoniste</t>
-  </si>
-  <si>
-    <t>G15_92</t>
-  </si>
-  <si>
-    <t>Orthoptiste</t>
-  </si>
-  <si>
-    <t>G15_94</t>
-  </si>
-  <si>
-    <t>Ergothérapeute</t>
-  </si>
-  <si>
-    <t>G15_95</t>
-  </si>
-  <si>
-    <t>Diététicien</t>
-  </si>
-  <si>
-    <t>G15_96</t>
-  </si>
-  <si>
-    <t>Psychomotricien</t>
-  </si>
-  <si>
-    <t>G15_98</t>
-  </si>
-  <si>
-    <t>Manipulateur ERM</t>
-  </si>
-  <si>
-    <t>G16_10</t>
-  </si>
-  <si>
-    <t>Médecin en formation</t>
-  </si>
-  <si>
-    <t>G16_21</t>
-  </si>
-  <si>
-    <t>Pharmacien en formation</t>
-  </si>
-  <si>
-    <t>G16_40</t>
-  </si>
-  <si>
-    <t>Chirurgien-Dentiste en formation</t>
-  </si>
-  <si>
-    <t>G16_50</t>
-  </si>
-  <si>
-    <t>Sage-Femme en formation</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A02-ProfessionSavFaire-CISIS/FHIR/TRE-A02-ProfessionSavFaire-CISIS</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>Ostéopathe</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>Psychothérapeute</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>Chiropracteur</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>Psychologue</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R95-UsagerTitre/FHIR/TRE-R95-UsagerTitre</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Assistant de service social</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R94-ProfessionSocial/FHIR/TRE-R94-ProfessionSocial</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>Assistant de service social (PAERPA)</t>
-  </si>
-  <si>
-    <t>301</t>
-  </si>
-  <si>
-    <t>Coordination territoriale d'appui (PAERPA)</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>Aide et accompagnement à domicile (PAERPA)</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>Avocat participant aux processus de soins sans consentement (eSSS)</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>Assistant de service social (Expérimentation MAIA)</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>Psychologue (Expérimentation MAIA)</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>Psychothérapeute (Expérimentation MAIA)</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Mandataire judiciaire à la protection des majeurs (MJPM)</t>
-  </si>
-  <si>
-    <t>308</t>
-  </si>
-  <si>
-    <t>Pilote MAIA</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>Gestionnaire de cas MAIA</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Equipe médico-sociale APA</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Autre acteur mettant en oeuvre la méthode MAIA</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>Autre professionnel</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>314</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>316</t>
-  </si>
-  <si>
     <t>317</t>
   </si>
   <si>
@@ -2399,6 +2363,12 @@
   </si>
   <si>
     <t>Assistant(e) maternel(le)</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>Membre de l'équipe de soins</t>
   </si>
   <si>
     <t>354</t>
@@ -2867,7 +2837,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B312"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -5356,82 +5326,18 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>665</v>
+        <v>44</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>666</v>
+        <v>44</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>667</v>
+        <v>45</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="B313" t="s" s="2">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="B314" t="s" s="2">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="B315" t="s" s="2">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B316" t="s" s="2">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="B317" t="s" s="2">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="B318" t="s" s="2">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B319" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B320" t="s" s="2">
-        <v>681</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>
@@ -5458,34 +5364,34 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>683</v>
+        <v>667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>685</v>
+        <v>669</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>686</v>
+        <v>670</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>687</v>
+        <v>671</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>689</v>
+        <v>673</v>
       </c>
     </row>
     <row r="6">
@@ -5501,7 +5407,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>690</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -5528,10 +5434,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>691</v>
+        <v>675</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>692</v>
+        <v>676</v>
       </c>
     </row>
     <row r="3">
@@ -5547,7 +5453,7 @@
         <v>45</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>693</v>
+        <v>677</v>
       </c>
     </row>
   </sheetData>
@@ -5557,7 +5463,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -5574,570 +5480,578 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>694</v>
+        <v>678</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>695</v>
+        <v>679</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>696</v>
+        <v>680</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>697</v>
+        <v>681</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>698</v>
+        <v>682</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>699</v>
+        <v>683</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>700</v>
+        <v>684</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>701</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>702</v>
+        <v>686</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>703</v>
+        <v>687</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>704</v>
+        <v>688</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>705</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>707</v>
+        <v>691</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>709</v>
+        <v>693</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>710</v>
+        <v>694</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>711</v>
+        <v>695</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>713</v>
+        <v>697</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>715</v>
+        <v>699</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>716</v>
+        <v>700</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>717</v>
+        <v>701</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>719</v>
+        <v>703</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>720</v>
+        <v>704</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>612</v>
+        <v>705</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>614</v>
+        <v>707</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>616</v>
+        <v>709</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>618</v>
+        <v>711</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>725</v>
+        <v>713</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>727</v>
+        <v>715</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>729</v>
+        <v>717</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>731</v>
+        <v>719</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>733</v>
+        <v>721</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>735</v>
+        <v>723</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>737</v>
+        <v>725</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>739</v>
+        <v>727</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>741</v>
+        <v>729</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>743</v>
+        <v>731</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>745</v>
+        <v>733</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>748</v>
+        <v>736</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>751</v>
+        <v>739</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>753</v>
+        <v>741</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>755</v>
+        <v>743</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>757</v>
+        <v>745</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>759</v>
+        <v>747</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>761</v>
+        <v>749</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>763</v>
+        <v>751</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>765</v>
+        <v>753</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>767</v>
+        <v>755</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>769</v>
+        <v>757</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>771</v>
+        <v>759</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>773</v>
+        <v>761</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>775</v>
+        <v>763</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>777</v>
+        <v>765</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>779</v>
+        <v>767</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>781</v>
+        <v>769</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>783</v>
+        <v>771</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>785</v>
+        <v>773</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>786</v>
+        <v>774</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>787</v>
+        <v>775</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>789</v>
+        <v>777</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>791</v>
+        <v>779</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>793</v>
+        <v>781</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>794</v>
+        <v>782</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>795</v>
+        <v>783</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>797</v>
+        <v>785</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>799</v>
+        <v>787</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>801</v>
+        <v>789</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>803</v>
+        <v>791</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>805</v>
+        <v>793</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>807</v>
+        <v>795</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>809</v>
+        <v>797</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>811</v>
+        <v>799</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>813</v>
+        <v>801</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>815</v>
+        <v>803</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>816</v>
+        <v>804</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>817</v>
+        <v>805</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>818</v>
+        <v>806</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>819</v>
+        <v>807</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>821</v>
+        <v>809</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>823</v>
+        <v>811</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>825</v>
+        <v>813</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>827</v>
+        <v>815</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>44</v>
+        <v>816</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>44</v>
+        <v>817</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="B72" t="s" s="2">
-        <v>828</v>
+      <c r="B73" t="s" s="2">
+        <v>818</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
@@ -1405,7 +1405,7 @@
     <t>G15_10/DEC05</t>
   </si>
   <si>
-    <t>Médecin - Cancérologie option chiruggie cancérologique (DEC)</t>
+    <t>Médecin - Cancérologie option chirurgie cancérologique (DEC)</t>
   </si>
   <si>
     <t>G15_10/DEC06</t>
